--- a/Assets/Excal/MonsterInfo.xlsx
+++ b/Assets/Excal/MonsterInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9767"/>
+    <workbookView windowWidth="22185" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1020,14 +1020,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.44444444444444" customWidth="1"/>
-    <col min="2" max="2" width="11.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="8.44166666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.8916666666667" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="5" max="5" width="10.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="11.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="10.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="10.775" customWidth="1"/>
+    <col min="6" max="6" width="11.8916666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1070,7 +1070,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1">
         <v>100</v>
@@ -1099,7 +1099,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1">
         <v>110</v>
@@ -1128,7 +1128,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1">
         <v>120</v>
@@ -1157,7 +1157,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>150</v>
@@ -1186,13 +1186,13 @@
         <v>6</v>
       </c>
       <c r="E6" s="1">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>60</v>
       </c>
       <c r="G6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1">
         <v>0.9</v>
@@ -1215,13 +1215,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="1">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
         <v>140</v>
       </c>
       <c r="G7" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1">
         <v>0.88</v>
@@ -1244,13 +1244,13 @@
         <v>8</v>
       </c>
       <c r="E8" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
         <v>200</v>
       </c>
       <c r="G8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1">
         <v>0.6</v>
@@ -1283,7 +1283,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1295,7 +1295,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
